--- a/NovaSaaS_LBO_Model.xlsx
+++ b/NovaSaaS_LBO_Model.xlsx
@@ -192,7 +192,7 @@
     <t xml:space="preserve">NovaSaaS Inc.  ·  Radice Capital Partners</t>
   </si>
   <si>
-    <t xml:space="preserve">Entry EV $485m  ·  18.5x LTM EBITDA  ·  June 2026</t>
+    <t xml:space="preserve">Entry EV $485m  ·  18.5x LTM EBITDA  ·  March 2026</t>
   </si>
   <si>
     <t xml:space="preserve">5-Year Hold  ·  Base Gross IRR 24.0%  ·  MoM 2.9x  ·  Net IRR 20.5%</t>
@@ -237,7 +237,7 @@
     <t xml:space="preserve">Notes (grey)  — commentary, not model inputs</t>
   </si>
   <si>
-    <t xml:space="preserve">Prepared by: Alessandro Radice  ·  June 2026  ·  Fictional case study — all data hypothetical</t>
+    <t xml:space="preserve">Prepared by: Alessandro Radice  ·  March 2026  ·  Fictional case study — all data hypothetical</t>
   </si>
   <si>
     <t xml:space="preserve">ASSUMPTIONS  &amp;  SOURCES / USES</t>

--- a/NovaSaaS_LBO_Model.xlsx
+++ b/NovaSaaS_LBO_Model.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="Calc"/>
+  <fileVersion appName="xl"/>
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
@@ -17,11 +17,6 @@
     <sheet name="Sensitivity" sheetId="7" state="visible" r:id="rId9"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
-  <extLst>
-    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
-      <loext:extCalcPr stringRefSyntax="ExcelA1"/>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
@@ -198,7 +193,7 @@
     <t xml:space="preserve">5-Year Hold  ·  Base Gross IRR 24.0%  ·  MoM 2.9x  ·  Net IRR 20.5%</t>
   </si>
   <si>
-    <t xml:space="preserve">STRICTLY CONFIDENTIAL — NOT FOR DISTRIBUTION</t>
+    <t xml:space="preserve">PRIVATE &amp; CONFIDENTIAL · FICTIONAL CASE STUDY</t>
   </si>
   <si>
     <t xml:space="preserve">TABLE OF CONTENTS</t>
@@ -225,19 +220,19 @@
     <t xml:space="preserve">COLOUR CODING</t>
   </si>
   <si>
-    <t xml:space="preserve">Hardcoded inputs (blue)  — user-editable assumptions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cross-sheet links (green) — auto-populated from other tabs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Formulas (black)  — calculated cells, do not override</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Notes (grey)  — commentary, not model inputs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prepared by: Alessandro Radice  ·  March 2026  ·  Fictional case study — all data hypothetical</t>
+    <t xml:space="preserve">Hardcoded inputs (blue): user-editable assumptions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cross-sheet links (green): auto-populated from other tabs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Formulas (black): calculated cells, do not override</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Notes (grey): commentary, not model inputs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prepared by: Alessandro Radice  ·  March 2026  ·  Fictional case study, all data hypothetical</t>
   </si>
   <si>
     <t xml:space="preserve">ASSUMPTIONS  &amp;  SOURCES / USES</t>
@@ -546,7 +541,7 @@
     <t xml:space="preserve">Opening Balance (bullet)</t>
   </si>
   <si>
-    <t xml:space="preserve">  PIK NOTES  (8.5% — Toggle · accretes)</t>
+    <t xml:space="preserve">  PIK NOTES  (8.5% · Toggle · accretes)</t>
   </si>
   <si>
     <t xml:space="preserve">PIK Accrual (8.5% on opening)</t>
@@ -636,10 +631,10 @@
     <t xml:space="preserve">Benchmark</t>
   </si>
   <si>
-    <t xml:space="preserve">Invested Equity — Sponsor ($mm)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">—</t>
+    <t xml:space="preserve">Invested Equity: Sponsor ($mm)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">–</t>
   </si>
   <si>
     <t xml:space="preserve">Gross MoM</t>
@@ -732,10 +727,10 @@
     <t xml:space="preserve">TOTAL = Sponsor Exit Equity</t>
   </si>
   <si>
-    <t xml:space="preserve">SENSITIVITY ANALYSIS — IRR &amp; MoM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  GROSS IRR — Entry Multiple (rows) × Exit Multiple (cols)</t>
+    <t xml:space="preserve">SENSITIVITY ANALYSIS: IRR &amp; MoM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  GROSS IRR: Entry Multiple (rows) × Exit Multiple (cols)</t>
   </si>
   <si>
     <t xml:space="preserve">Entry ↓ / Exit →</t>
@@ -771,7 +766,7 @@
     <t xml:space="preserve">20.5x</t>
   </si>
   <si>
-    <t xml:space="preserve">  MONEY-ON-MONEY — Entry × Exit</t>
+    <t xml:space="preserve">  MONEY-ON-MONEY: Entry × Exit</t>
   </si>
   <si>
     <t xml:space="preserve">  LEGEND (darker = higher return)  ·  ★ = base case</t>

--- a/NovaSaaS_LBO_Model.xlsx
+++ b/NovaSaaS_LBO_Model.xlsx
@@ -184,7 +184,7 @@
     <t xml:space="preserve">LEVERAGED BUYOUT MODEL</t>
   </si>
   <si>
-    <t xml:space="preserve">NovaSaaS Inc.  ·  Radice Capital Partners</t>
+    <t xml:space="preserve">NovaSaaS Inc.  ·  Buy-side LBO case study</t>
   </si>
   <si>
     <t xml:space="preserve">Entry EV $485m  ·  18.5x LTM EBITDA  ·  March 2026</t>
